--- a/data_extactor/batch_10_fa/batch_0037_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0037_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Captivate | Adobe Connect | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Adobe Presenter | Adobe RoboHelp | Adobe eLearning Suite | Apple Final Cut Pro | Apple QuickTime | Articulate 360 | Articulate Rapid E-Learning Studio | Articulate Storyline | Audacity | Avid Technology Pinnacle Studio | Blackboard Learn | نرم‌افزار Blackboard | نرم‌افزار Cascading style sheets CSS | Common Curriculum | Corel WordPerfect Office Suite | Cornerstone OnDemand Cornerstone Learning | نرم‌افزار Desire2Learn LMS | Drupal | نرم‌افزار Dynamic hypertext markup language DHTML | EasyCBM | Edmodo | Edpuzzle | Elucidat | نرم‌افزار ایمیل | نرم‌افزار Extensible hypertext markup language XHTML | نرم‌افزار Extensible markup language XML | Flipgrid | Google Classroom | نرم‌افزار مدیریت منابع انسانی HRMS | نرم‌افزار Hypertext markup language HTML | IBM Lotus 1-2-3 | IXL Learning Quia Web | Instructure Canvas | JavaScript | Kahoot! | Learning Technology Research Institute GLO Maker | نرم‌افزار سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | Microsoft Office FrontPage | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Moodle | Nvu | Oracle Java | Oracle PL/SQL | Performance Technology Associates DocuTools | Poll Everywhere | Quizlet | Schoology | Screencast-O-Matic | SeaMonkey | Seesaw | SmartDraw VP | SoftChalk LessonBuilder | Sony Sound Forge | نرم‌افزار Structured query language SQL | Suddenly Smart SmartBuilder | SumTotal Systems ToolBook | TechSmith Camtasia | TechSmith Snagit | Trivantis CourseMill | Trivantis Lectora | Vasont Content Management System | WeVideo | نرم‌افزار مرورگر وب | نرم‌افزار وبینار | Worldwide Instructional Design System WIDS | etouches</t>
+          <t>Adobe Acrobat | Adobe ActionScript | Adobe After Effects | Adobe Captivate | Adobe Connect | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Adobe Presenter | Adobe RoboHelp | Adobe eLearning Suite | Apple Final Cut Pro | Apple QuickTime | Articulate 360 | Articulate Rapid E-Learning Studio | Articulate Storyline | Audacity | Avid Technology Pinnacle Studio | Blackboard Learn | نرم‌افزار Blackboard | برگه‌های سبک آبشاری CSS | Common Curriculum | Corel WordPerfect Office Suite | Cornerstone OnDemand Cornerstone Learning | نرم‌افزار Desire2Learn LMS | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | EasyCBM | Edmodo | Edpuzzle | Elucidat | نرم‌افزار ایمیل | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Flipgrid | Google Classroom | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Lotus 1-2-3 | IXL Learning Quia Web | Instructure Canvas | JavaScript | Kahoot! | Learning Technology Research Institute GLO Maker | سیستم مدیریت یادگیری LMS | Microsoft Access | Microsoft Excel | Microsoft Office FrontPage | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | Moodle | Nvu | Oracle Java | Oracle PL/SQL | Performance Technology Associates DocuTools | Poll Everywhere | Quizlet | Schoology | Screencast-O-Matic | SeaMonkey | Seesaw | SmartDraw VP | SoftChalk LessonBuilder | Sony Sound Forge | زبان پرس‌وجوی ساختاریافته SQL | Suddenly Smart SmartBuilder | SumTotal Systems ToolBook | TechSmith Camtasia | TechSmith Snagit | Trivantis CourseMill | Trivantis Lectora | Vasont Content Management System | WeVideo | نرم‌افزار مرورگر وب | نرم‌افزار وبینار | Worldwide Instructional Design System WIDS | etouches</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | نوشتن | صحبت کردن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | نگارش | سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | ریاضیات | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | فلسفه و الهیات | روان‌شناسی | اداری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | فلسفه و الهیات | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | دید نزدیک | انعطاف‌پذیری دسته‌بندی | خلاقیت | استدلال استقرایی | نظم‌دهی اطلاعات | روانی ایده‌ها | دید دور | حافظه | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | توجه انتخابی | تجسم</t>
+          <t>درک کتبی | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بینایی دور | حفظ کردن | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های رودررو با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | سخنرانی عمومی | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، مقطع پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | مدیران آموزشی، مهدکودک تا متوسطه | معلمان آموزشی، مقطع پس از متوسطه | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدیران آموزشی، مهدکودک تا دبیرستان | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | مدیران آموزش و توسعه | متخصصان آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی</t>
+          <t>دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی (Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Appletree | Automate the Schools ATS | نرم‌افزار Blackboard | نرم‌افزار آموزشی کودکان | ClassDojo | نرم‌افزار ایمیل | Flipgrid | Google Classroom | Google Meet | غلط‌یاب‌های املایی دستی | High School Scheduling and Transcript HSST | Kahoot! | Loom | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | ParentSquare | Quizlet | Schoology | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Seesaw | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | Tadpoles | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار مرورگر وب</t>
+          <t>Appletree | Automate the Schools ATS | نرم‌افزار Blackboard | Children's educational software | ClassDojo | نرم‌افزار ایمیل | Flipgrid | Google Classroom | Google Meet | غلط‌یاب‌های املایی دستی | High School Scheduling and Transcript HSST | Kahoot! | Loom | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | ParentSquare | Quizlet | Schoology | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Seesaw | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | Tadpoles | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | صحبت کردن | نوشتن | تفکر انتقادی | استراتژی‌های یادگیری | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | ریاضیات | آموزش و پرورش | ایمنی و امنیت عمومی | اداری | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | ریاضیات | آموزش و پرورش | ایمنی و امنیت عمومی | اداری | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | نظم‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان نوشتاری | دید دور | دید نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | روانی ایده‌ها | خلاقیت | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | بینایی دور | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | روانی ایده‌ها | اصالت | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تکرار تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | بحث‌های رودررو با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | مدیران آموزشی، مهدکودک تا متوسطه | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان مهدکودک، به جز آموزش استثنایی | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان پیش‌دبستانی، به جز آموزش استثنایی | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان خودآموزی | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، پیش‌دبستانی | معلمان آموزش استثنایی، متوسطه | معلمان جایگزین، کوتاه‌مدت | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | مدیران آموزشی، مهدکودک تا دبیرستان | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان خودسازی | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | معلمان جایگزین، کوتاه‌مدت | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>دستیاران آموزشی، آموزش استثنایی</t>
+          <t>دستیاران آموزشی، آموزش استثنایی (Teaching Assistants, Special Education)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Appletree | Automate the Schools ATS | نرم‌افزار Blackboard | نرم‌افزار آموزشی کودکان | ClassDojo | نرم‌افزار ایمیل | Flipgrid | Google Classroom | Google Meet | غلط‌یاب‌های املایی دستی | High School Scheduling and Transcript HSST | Kahoot! | Loom | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | ParentSquare | Quizlet | Schoology | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Seesaw | سیستم اطلاعات دانش‌آموزی آموزش استثنایی SESIS | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | Tadpoles | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار مرورگر وب</t>
+          <t>Appletree | Automate the Schools ATS | نرم‌افزار Blackboard | Children's educational software | ClassDojo | نرم‌افزار ایمیل | Flipgrid | Google Classroom | Google Meet | غلط‌یاب‌های املایی دستی | High School Scheduling and Transcript HSST | Kahoot! | Loom | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Padlet | ParentSquare | Quizlet | Schoology | نرم‌افزار بزرگ‌نمایی صفحه | نرم‌افزار صفحه‌خوان | Seesaw | سیستم اطلاعات دانش‌آموزی آموزش استثنایی SESIS | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | Tadpoles | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | استراتژی‌های یادگیری | نظارت | تفکر انتقادی | نوشتن | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نظارت | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | درک نوشتاری | استدلال قیاسی | نظم‌دهی اطلاعات | بیان نوشتاری | روانی ایده‌ها | توجه شنیداری | توجه انتخابی | استدلال استقرایی | خلاقیت | اشتراک زمان | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | روانی ایده‌ها | توجه شنیداری | توجه انتخابی | استدلال استقرایی | اصالت | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | نزدیکی فیزیکی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تکرار تصمیم‌گیری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | ایمیل | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، مقطع پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | معلمان آموزشی، مقطع پس از متوسطه | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان مهدکودک، به جز آموزش استثنایی | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، پیش‌دبستانی | معلمان آموزش استثنایی، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | مدیران آموزش و توسعه | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | اساتید آموزش‌های شغلی/فنی، پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، مقطع پس از متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | مدیران آموزش و توسعه | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>دستیاران آموزشی، مقطع پس از متوسطه</t>
+          <t>دستیاران آموزشی، مقطع پس از متوسطه (Teaching Assistants, Postsecondary)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAS | Sakai CLE | نرم‌افزار Structured query language SQL | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
+          <t>Adobe Photoshop | Blackboard Learn | نرم‌افزار ویرایش مشارکتی | نرم‌افزار سیستم مدیریت دوره | DOC Cop | نرم‌افزار Desire2Learn LMS | نرم‌افزار ایمیل | Google Docs | IBM SPSS Statistics | نرم‌افزار اسکن تصویر | سیستم مدیریت یادگیری LMS | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | SAS | Sakai CLE | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مرورگر وب | iParadigms Turnitin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | استراتژی‌های یادگیری | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | وضوح گفتار | بیان نوشتاری | دید نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | خلاقیت | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | بینایی نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | اصالت | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | سخنرانی عمومی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | سطح رقابت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | سخنرانی عمومی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | سطح رقابت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | معلمان علوم زیستی، مقطع پس از متوسطه | معلمان آموزش فنی/حرفه‌ای، مقطع راهنمایی | معلمان آموزش فنی/حرفه‌ای، مقطع متوسطه | معلمان آموزشی، مقطع پس از متوسطه | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | هماهنگ‌کنندگان آموزشی | معلمان علوم کتابداری، مقطع پس از متوسطه | معلمان علوم ریاضی، مقطع پس از متوسطه | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان روان‌شناسی، مقطع پس از متوسطه | معلمان مدرسه متوسطه، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان جامعه‌شناسی، مقطع پس از متوسطه | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، مهدکودک | معلمان آموزش استثنایی، راهنمایی | معلمان آموزش استثنایی، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
+          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و انگلیسی به عنوان زبان دوم | مدرسان علوم زیستی، پس از متوسطه | معلمان آموزش‌های شغلی/فنی، دوره راهنمایی | معلمان آموزش فنی/حرفه‌ای، دوره متوسطه | مدرسان علوم تربیتی، آموزش عالی | معلمان دبستان، به استثنای آموزش استثنایی | هماهنگ‌کنندگان آموزشی | مدرسان علوم کتابداری، آموزش عالی | مدرسان علوم ریاضی، پس از متوسطه | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | استادان روان‌شناسی، پس از متوسطه | معلمان دبیرستان، به استثنای آموزش ویژه و فنی/حرفه‌ای | استادان جامعه‌شناسی، پس از متوسطه | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، راهنمایی | معلمان آموزش ویژه، متوسطه | دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | معلمان خصوصی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>دستیاران آموزشی، سایر</t>
+          <t>دستیاران آموزشی، سایر (Teaching Assistants, All Other)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمان | مهارت انگشتان | مهارت دستی | دید دور | حافظه | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | تکرار تصمیم‌گیری | نزدیکی فیزیکی | اهمیت تکرار کارهای مشابه</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | صرف زمان برای ایستادن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی | معلمان جایگزین، کوتاه‌مدت | معلمان خودآموزی | معلمان مدرسه ابتدایی، به جز آموزش استثنایی | معلمان پیش‌دبستانی، به جز آموزش استثنایی | معلمان مهدکودک، به جز آموزش استثنایی | معلمان مدرسه راهنمایی، به جز آموزش استثنایی و فنی/حرفه‌ای | معلمان آموزش استثنایی، ابتدایی | معلمان آموزش استثنایی، سایر | تکنسین‌های کتابخانه | کتابداران و متخصصان مجموعه‌های رسانه‌ای | کارکنان مراقبت از کودکان | دستیاران خدمات اجتماعی و انسانی | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | هماهنگ‌کنندگان آموزشی | معلمان و مربیان، سایر | کارکنان آموزش و کتابداری، سایر</t>
+          <t>دستیاران آموزشی، پیش‌دبستانی، ابتدایی، راهنمایی و متوسطه، به جز آموزش استثنایی | دستیاران آموزشی، آموزش استثنایی | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی | معلمان جایگزین، کوتاه‌مدت | معلمان خودسازی | معلمان دبستان، به استثنای آموزش استثنایی | مربیان پیش‌دبستانی، به استثنای آموزش استثنایی | مربیان کودکستان، به استثنای آموزش استثنایی | معلمان دوره راهنمایی، به استثنای آموزش استثنایی و فنی/حرفه‌ای | معلمان آموزش ویژه، دبستان | معلمان آموزش ویژه، سایر موارد | تکنسین‌های کتابخانه | کتابداران و متخصصان مجموعه‌های رسانه‌ای | مربیان و کارکنان مراقبت از کودکان | دستیاران خدمات اجتماعی و انسانی | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | هماهنگ‌کنندگان آموزشی | معلمان و مربیان، سایر | کارکنان آموزش و کتابداری، سایر</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>کارکنان آموزش و کتابداری، سایر</t>
+          <t>کارکنان آموزش و کتابداری، سایر (Educational Instruction and Library Workers, All Other)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نظارت | نوشتن</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | کامپیوتر و الکترونیک | مدیریت و اداره | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمان | مهارت انگشتان | مهارت دستی | دید دور | حافظه | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تکرار تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | اهمیت تکرار کارهای مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کتابخانه | کتابداران و متخصصان مجموعه‌های رسانه‌ای | آرشیوداران | متصدیان | تکنسین‌های موزه و محافظان | هماهنگ‌کنندگان آموزشی | دستیاران آموزشی، سایر | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی | معلمان خودآموزی | معلمان جایگزین، کوتاه‌مدت | معلمان و مربیان، سایر | مدیران آموزشی، سایر | مدیران آموزشی، مقطع پس از متوسطه | مشاوران و راهنمایان آموزشی، تحصیلی و شغلی | متخصصان آموزش و توسعه | متخصصان مدیریت اسناد | کارمندان اداری، عمومی | اطلاعات و کارمندان ثبت، سایر | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>تکنسین‌های کتابخانه | کتابداران و متخصصان مجموعه‌های رسانه‌ای | آرشیوچی‌ها | موزه‌داران | تکنسین‌ها و محافظان موزه | هماهنگ‌کنندگان آموزشی | دستیاران آموزشی، سایر | دستیاران آموزشی، مقطع پس از متوسطه | معلمان خصوصی | معلمان خودسازی | معلمان جایگزین، کوتاه‌مدت | معلمان و مربیان، سایر | مدیران آموزشی، سایر | مدیران آموزشی، پس از متوسطه | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | متخصصان آموزش و توسعه | متخصصان مدیریت اسناد | کارمندان دفتری عمومی | کارمندان اطلاعات و ثبت سوابق، سایر | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Dreamweaver | Adobe Illustrator | Adobe ImageReady | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apache Flex | Apple Final Cut Pro | Apple Keynote | Apple iWork Keynote | Apple macOS | Atlassian Confluence | Atlassian JIRA | Autodesk 3ds Max Design | Autodesk Maya | نرم‌افزار Cascading style sheets CSS | نرم‌افزار طراحی به کمک رایانه | نرم‌افزار تجسم داده‌ها | Drupal | نرم‌افزار Dynamic hypertext markup language DHTML | نرم‌افزار Extensible hypertext markup language XHTML | Facebook | Figma | Google Slides | نرم‌افزار Hypertext markup language HTML | JavaScript | Mag+ | Maxon Cinema 4D | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار کاربردی موبایل | PHP | نرم‌افزار نشر سازمانی Quark | QuarkXPress | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار کاربردی تبلت | نرم‌افزار طراحی رابط کاربری | WeVideo | نرم‌افزار مرورگر وب | WoodWing | WordPress | YouTube | jQuery</t>
+          <t>AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Dreamweaver | Adobe Illustrator | Adobe ImageReady | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Apache Flex | Apple Final Cut Pro | Apple Keynote | Apple iWork Keynote | Apple macOS | Atlassian Confluence | Atlassian JIRA | Autodesk 3ds Max Design | Autodesk Maya | برگه‌های سبک آبشاری CSS | نرم‌افزار طراحی به کمک کامپیوتر | نرم‌افزار تجسم داده | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | Facebook | Figma | Google Slides | زبان نشانه‌گذاری ابرمتن HTML | JavaScript | Mag+ | Maxon Cinema 4D | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار اپلیکیشن موبایل | PHP | نرم‌افزار نشر سازمانی Quark | QuarkXPress | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار کاربردی تبلت | نرم‌افزار طراحی رابط کاربری | WeVideo | نرم‌افزار مرورگر وب | WoodWing | WordPress | YouTube | jQuery</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | صحبت کردن | درک مطلب | تفکر انتقادی | نوشتن | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | زبان انگلیسی | کامپیوتر و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | فروش و بازاریابی | خدمات مشتری و شخصی</t>
+          <t>طراحی | زبان انگلیسی | رایانه و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | فروش و بازاریابی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>خلاقیت | روانی ایده‌ها | درک شفاهی | درک نوشتاری | بیان شفاهی | دید نزدیک | تجسم | حساسیت به مسئله | نظم‌دهی اطلاعات | تشخیص رنگ بصری | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان نوشتاری | دید دور | انعطاف‌پذیری بستار</t>
+          <t>اصالت | روانی ایده‌ها | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تجسم | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای نشستن | ایمیل | محیط داخلی، دارای کنترل محیطی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | تکرار تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای نشستن | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | طراحان مد | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | طراحان گرافیک | مدیران پروژه فناوری اطلاعات | مدیران برنامه‌نویسی رسانه | مدیران فنی رسانه | نمایش‌دهندگان کالا و تزئین‌کنندگان ویترین | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | متخصصان روابط عمومی | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | نویسندگان فنی | طراحان بازی‌های ویدئویی | طراحان وب و رابط دیجیتال | نویسندگان و مؤلفان</t>
+          <t>هنرمندان صنایع دستی | طراحان مد | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | طراحان گرافیک | مدیران پروژه فناوری اطلاعات | مدیران برنامه‌ریزی رسانه | مدیران/کارگردانان فنی رسانه | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | متخصصان مدیریت پروژه | متخصصان روابط عمومی | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | نویسندگان فنی | طراحان بازی‌های ویدئویی | طراحان رابط دیجیتال و وب | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی</t>
+          <t>هنرمندان صنایع دستی (Craft Artists)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | صحبت کردن | گوش دادن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | هنرهای زیبا | فروش و بازاریابی | زبان انگلیسی | خدمات مشتری و شخصی | تولید و پردازش</t>
+          <t>طراحی | هنرهای زیبا | فروش و بازاریابی | زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>خلاقیت | ثبات بازو-دست | مهارت انگشتان | مهارت دستی | دید نزدیک | روانی ایده‌ها | تجسم | هماهنگی چند اندام | دقت کنترل | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | درک نوشتاری | درک شفاهی | بیان شفاهی</t>
+          <t>اصالت | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | بینایی نزدیک | روانی ایده‌ها | تجسم | هماهنگی چند عضو | دقت کنترل | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | درک شفاهی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن</t>
+          <t>تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران نیمکت | طراحان تجاری و صنعتی | حکاکان | الگوسازان پارچه و پوشاک | طراحان مد | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | پرداخت‌کنندگان مبلمان | طراحان گرافیک | طراحان داخلی | جواهرسازان و کارگران سنگ‌های قیمتی و فلزات | مدل‌سازان، چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزئین | الگوسازان، فلز و پلاستیک | الگوسازان، چوب | سفالگران، تولیدی | طراحان صحنه و نمایشگاه | دوزندگان، دستی | کارگران کفش و چرم و تعمیرکاران | سنگ‌تراشان و حکاکان، تولیدی</t>
+          <t>کابینت‌سازان و نجاران نیمکت | طراحان تجاری و صنعتی | حکاکان و تیزاب‌کاران | الگوسازان پارچه و پوشاک | طراحان مد | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | پرداخت‌کاران مبلمان | طراحان گرافیک | طراحان داخلی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | سفالگران، تولیدی | طراحان صحنه و نمایشگاه | دوزندگان دستی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران</t>
+          <t>هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران (Fine Artists, Including Painters, Sculptors, and Illustrators)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe ImageReady | Adobe InDesign | Adobe Photoshop | ArtScope.net eArtist | Autodesk 3D Studio Design | Autodesk AutoCAD | Autodesk Maya | C# | C++ | Camp Software Art Licensing Manager | ClassDojo | Code Line Art Files | Corel CorelDraw Graphics Suite | Corel Paint Shop Pro | Corel Painter | Corel Photo-Paint | نرم‌افزار پردازش کارت اعتباری | Dassault Systemes CATIA | نرم‌افزار ایمیل | نرم‌افزار Extensible markup language XML | Facebook | FileMaker Bento | GYST | GroupMe | نرم‌افزار Hypertext markup language HTML | Inkscape | Intuit QuickBooks | JavaScript | نرم‌افزار Microsoft Office | Microsoft Paint | Microsoft PowerPoint | Microsoft Word | Paintbrush | نرم‌افزار Perforce Helix | Pixologic Zbrush | Python | Serif DrawPlus | SmugMug Flickr | Trimble SketchUp Pro | Twitter | Unity Technologies Unity | Unreal Technology Unreal Engine | نرم‌افزار مرورگر وب | WorkingArtist Systems WorkingArtist | Xara Designer Pro X</t>
+          <t>Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe ImageReady | Adobe InDesign | Adobe Photoshop | ArtScope.net eArtist | Autodesk 3D Studio Design | Autodesk AutoCAD | Autodesk Maya | C# | C++ | Camp Software Art Licensing Manager | ClassDojo | Code Line Art Files | Corel CorelDraw Graphics Suite | Corel Paint Shop Pro | Corel Painter | Corel Photo-Paint | نرم‌افزار پردازش کارت اعتباری | Dassault Systemes CATIA | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | Facebook | FileMaker Bento | GYST | GroupMe | زبان نشانه‌گذاری ابرمتن HTML | Inkscape | Intuit QuickBooks | JavaScript | نرم‌افزار Microsoft Office | Microsoft Paint | Microsoft PowerPoint | Microsoft Word | Paintbrush | نرم‌افزار Perforce Helix | Pixologic Zbrush | Python | Serif DrawPlus | SmugMug Flickr | Trimble SketchUp Pro | Twitter | Unity Technologies Unity | Unreal Technology Unreal Engine | نرم‌افزار مرورگر وب | WorkingArtist Systems WorkingArtist | Xara Designer Pro X</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | گوش دادن فعال | صحبت کردن | درک مطلب</t>
+          <t>یادگیری فعال | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | کامپیوتر و الکترونیک | زبان انگلیسی | تولید و پردازش | هنرهای زیبا | آموزش و پرورش | ارتباطات و رسانه | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره</t>
+          <t>طراحی | رایانه و الکترونیک | زبان انگلیسی | تولید و فرآوری | هنرهای زیبا | آموزش و پرورش | ارتباطات و رسانه | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>خلاقیت | روانی ایده‌ها | تجسم | ثبات بازو-دست | تشخیص رنگ بصری | دید نزدیک | مهارت انگشتان | مهارت دستی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | نظم‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | دید دور | درک نوشتاری</t>
+          <t>اصالت | روانی ایده‌ها | تجسم | ثبات دست و بازو | تشخیص رنگ بصری | بینایی نزدیک | مهارت انگشتان | مهارت دستی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | بینایی دور | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا درست بودن | ایمیل | صرف زمان برای انجام حرکات تکراری | تکرار تصمیم‌گیری</t>
+          <t>آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | ایمیل | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | ناشران رومیزی | حکاکان | الگوسازان پارچه و پوشاک | طراحان مد | طراحان گرافیک | طراحان داخلی | هنرمندان آرایش، تئاتری و اجرایی | نقاشان، ساخت و نگهداری | کارگران نقاشی، پوشش‌دهی و تزئین | الگوسازان، فلز و پلاستیک | عکاسان | کارگران فرآیند عکاسی و اپراتورهای ماشین پردازش | شاعران، ترانه‌سرایان و نویسندگان خلاق | تکنسین‌ها و کارگران پیش از چاپ | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان بازی‌های ویدئویی</t>
+          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | ناشران رومیزی | حکاکان و تیزاب‌کاران | الگوسازان پارچه و پوشاک | طراحان مد | طراحان گرافیک | طراحان داخلی | میکاپ آرتیست‌های تئاتر و نمایش | نقاشان، ساختمان و نگهداری | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | عکاسان | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | شاعران، ترانه‌سرایان و نویسندگان خلاق | تکنسین‌ها و کارگران پیش از چاپ | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان بازی‌های ویدئویی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>هنرمندان جلوه‌های ویژه و انیماتورها</t>
+          <t>هنرمندان جلوه‌های ویژه و انیماتورها (Special Effects Artists and Animators)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ACD Systems Canvas | AJAX | Ability Photopaint | Adobe AIR | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Dreamweaver | Adobe Flex | Adobe FreeHand MX | Adobe Illustrator | Adobe ImageReady | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Ambient Design ArtRage | Apple DrawBerry | Apple Final Cut Pro | Apple macOS | Aqsis Renderer | AutoDesSys form Z | AutoQ3D | Autodesk 3ds Max | Autodesk 3ds Max Design | Autodesk Alias Design | Autodesk Alias Surface | Autodesk AutoCAD Civil 3D | Autodesk Combustion | Autodesk Maya | Autodesk MotionBuilder | Autodesk Mudbox | Autodesk SketchBook Pro | Autodesk SoftImage | Blender | Bohemian Coding DrawIt | Bunkspeed HyperDrive | Bunkspeed HyperMove | C | C++ | Caligari Corporation trueSpace | Canva | نرم‌افزار Cascading style sheets CSS | Celsys RETAS | Chaos Group V-Ray | Character Studio | Cheetah3D | کتابخانه‌های کد | کتابخانه‌های مؤلفه | Corel CorelDraw Graphics Suite | Corel Painter | Crytek CryEngine | Cybermotion 3D Designer | DAZ Productions Bryce | DAZ Productions Carrara | DX Studio | Drupal | نرم‌افزار Dynamic hypertext markup language DHTML | Electric Rain Swift 3D Xpress | نرم‌افزار Extensible hypertext markup language XHTML | نرم‌افزار Extensible markup language XML | Figma | Freeverse Lineform | Google Sites | HASH Animation:Master | نرم‌افزار Hypertext markup language HTML | Indigo Renderer | Inivis AC3D | JavaScript | Luxology Modo | Luxrender | MagicTracer | Massive Jet | MaxScript | Maxon BodyPaint 3D | Maxon Cinema 4D | Maya Embedded Language MEL | Mental Images Mental Ray | Microsoft Excel | Microsoft Expression Design | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Silverlight | Microsoft Visio | Microsoft Windows | Microsoft Word | NVDIA Gelato | Nevercenter Silo | NewTek Lightwave 3D | Next Limit Maxwell Render | NodeBox | زبان‌های برنامه‌نویسی شیءگرا | PHP | نرم‌افزار Perforce Helix | Pixar RenderMan Studio | Pixarra TwistedBrush | Pixelmator | Pixologic Zbrush | Python | Quad Software Grome | QuarkXPress | RealFlow | Satori Paint | Serif DrawPlus | Side Effects Software Houdini | SideFX Houdini | Skencil | SmithMicro Anime Studio | SmithMicro Manga Studio | SmithMicro SoftwarePoser | سایت‌های رسانه‌های اجتماعی | SplutterFish Brazil | Sunflow Render System | TechSmith Camtasia | نرم‌افزار گرافیک سه‌بعدی | Trapcode Particular | Trimble SketchUp Pro | نرم‌افزار گرافیک دوبعدی | UNIX | Unity Technologies Unity | Unreal Technology Unreal Engine | VectorDesigner | XML User Interface XUI | Xara Designer Pro | YouTube | e-on software Vue | jQuery | sK1 | solidThinking</t>
+          <t>ACD Systems Canvas | AJAX | Ability Photopaint | Adobe AIR | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Dreamweaver | Adobe Flex | Adobe FreeHand MX | Adobe Illustrator | Adobe ImageReady | Adobe InDesign | Adobe Photoshop | Adobe Premiere Pro | Ambient Design ArtRage | Apple DrawBerry | Apple Final Cut Pro | Apple macOS | Aqsis Renderer | AutoDesSys form Z | AutoQ3D | Autodesk 3ds Max | Autodesk 3ds Max Design | Autodesk Alias Design | Autodesk Alias Surface | Autodesk AutoCAD Civil 3D | Autodesk Combustion | Autodesk Maya | Autodesk MotionBuilder | Autodesk Mudbox | Autodesk SketchBook Pro | Autodesk SoftImage | Blender | Bohemian Coding DrawIt | Bunkspeed HyperDrive | Bunkspeed HyperMove | C | C++ | Caligari Corporation trueSpace | Canva | برگه‌های سبک آبشاری CSS | Celsys RETAS | Chaos Group V-Ray | Character Studio | Cheetah3D | کتابخانه‌های کد | کتابخانه‌های مؤلفه | Corel CorelDraw Graphics Suite | Corel Painter | Crytek CryEngine | Cybermotion 3D Designer | DAZ Productions Bryce | DAZ Productions Carrara | DX Studio | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Electric Rain Swift 3D Xpress | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | Figma | Freeverse Lineform | Google Sites | HASH Animation:Master | زبان نشانه‌گذاری ابرمتن HTML | Indigo Renderer | Inivis AC3D | JavaScript | Luxology Modo | Luxrender | MagicTracer | Massive Jet | MaxScript | Maxon BodyPaint 3D | Maxon Cinema 4D | Maya Embedded Language MEL | Mental Images Mental Ray | Microsoft Excel | Microsoft Expression Design | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Silverlight | Microsoft Visio | Microsoft Windows | Microsoft Word | NVDIA Gelato | Nevercenter Silo | NewTek Lightwave 3D | Next Limit Maxwell Render | NodeBox | زبان‌های برنامه‌نویسی شیءگرا | PHP | نرم‌افزار Perforce Helix | Pixar RenderMan Studio | Pixarra TwistedBrush | Pixelmator | Pixologic Zbrush | Python | Quad Software Grome | QuarkXPress | RealFlow | Satori Paint | Serif DrawPlus | Side Effects Software Houdini | SideFX Houdini | Skencil | SmithMicro Anime Studio | SmithMicro Manga Studio | SmithMicro SoftwarePoser | سایت‌های رسانه‌های اجتماعی | SplutterFish Brazil | Sunflow Render System | TechSmith Camtasia | نرم‌افزار گرافیک سه‌بعدی | Trapcode Particular | Trimble SketchUp Pro | نرم‌افزار گرافیک دوبعدی | UNIX | Unity Technologies Unity | Unreal Technology Unreal Engine | VectorDesigner | XML User Interface XUI | Xara Designer Pro | YouTube | e-on software Vue | jQuery | sK1 | solidThinking</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | صحبت کردن | نوشتن | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | طراحی | ارتباطات و رسانه | خدمات مشتری و شخصی | فروش و بازاریابی | مخابرات | مهندسی و فناوری | تولید و پردازش | جغرافیا</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ارتباطات و رسانه | خدمات مشتری و شخصی | فروش و بازاریابی | مخابرات | مهندسی و فناوری | تولید و فرآوری | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | تجسم | دید نزدیک | استدلال قیاسی | تشخیص رنگ بصری | حساسیت به مسئله | وضوح گفتار | خلاقیت | بیان نوشتاری | نظم‌دهی اطلاعات | روانی ایده‌ها | استدلال استقرایی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تجسم | بینایی نزدیک | استدلال قیاسی | تشخیص رنگ بصری | حساسیت به مسئله | وضوح گفتار | اصالت | بیان کتبی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال استقرایی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | فشار زمانی | اهمیت دقیق یا درست بودن | تکرار تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | نتایج کاری و خروجی‌های سایر کارکنان | مکالمات تلفنی | ارتباط با دیگران | سطح رقابت | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | ارتباط با دیگران | سطح رقابت | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران هنری | تکنسین‌های صوتی و تصویری | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | طراحان تجاری و صنعتی | برنامه‌نویسان رایانه | هنرمندان صنایع دستی | ناشران رومیزی | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مدیران فنی رسانه | عکاسان | کارگران فرآیند عکاسی و اپراتورهای ماشین پردازش | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | طراحان بازی‌های ویدئویی | توسعه‌دهندگان وب | طراحان وب و رابط دیجیتال | نویسندگان و مؤلفان</t>
+          <t>مدیران هنری | تکنسین‌های صوتی و تصویری | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | طراحان تجاری و صنعتی | برنامه‌نویسان کامپیوتر | هنرمندان صنایع دستی | ناشران رومیزی | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مدیران/کارگردانان فنی رسانه | عکاسان | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | تکنسین‌ها و کارگران پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | طراحان بازی‌های ویدئویی | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0037_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0037_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | نگارش | سخن گفتن | نظارت | شنیدن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
+          <t>راهبردهای یادگیری | نگارش | سخن گفتن | نظارت | گوش دادن فعال | درک مطلب | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | فلسفه و الهیات | روان‌شناسی | امور اداری</t>
+          <t>آموزش و پرورش | زبان انگلیسی | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | پرسنل و منابع انسانی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | فلسفه و الهیات | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | استدلال استقرایی | مرتب‌سازی اطلاعات | روانی و سیالی ایده‌ها | دید دور | حافظه و به‌خاطرسپاری | انعطاف‌پذیری در ادراک الگوها | مهارت کار با اعداد | استدلال ریاضی | توجه انتخابی | تجسم فضایی</t>
+          <t>درک کتبی | بیان کتبی | بیان شفاهی | درک شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | اصالت | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بینایی دور | حفظ کردن | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به عنوان زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | استادان علوم تربیتی آموزش عالی | مشاوران تحصیلی، شغلی و تربیتی | آموزگاران دوره ابتدایی (به‌جز استثنایی) | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | دبیران دوره دوم متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | معلمان استثنایی دوره ابتدایی | معلمان استثنایی دوره پیش‌دبستانی | معلمان استثنایی دوره اول متوسطه | معلمان استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز استثنایی) | کمک‌معلمان آموزش استثنایی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی | مدرسان و معلمان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | راهبردهای یادگیری | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | ریاضیات | آموزش و تدریس | ایمنی و امنیت عمومی | امور اداری | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | ریاضیات | آموزش و پرورش | ایمنی و امنیت عمومی | اداری | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | دید دور | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | استدلال قیاسی | روانی و سیالی ایده‌ها | ابتکار و اصالت | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | بینایی دور | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | روانی ایده‌ها | اصالت | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به عنوان زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدیران آموزشی دوره‌های پیش‌دبستانی تا متوسطه | مشاوران تحصیلی، شغلی و تربیتی | آموزگاران دوره ابتدایی (به‌جز استثنایی) | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مربیان پیش‌دبستانی (به‌جز استثنایی) | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | مربیان مهدکودک (به‌جز استثنایی) | دبیران دوره دوم متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | مدرسان دوره‌های آزاد و مهارت‌آموزی | معلمان استثنایی دوره ابتدایی | معلمان استثنایی دوره پیش‌دبستانی | معلمان استثنایی دوره اول متوسطه | معلمان استثنایی دوره مهدکودک | معلمان استثنایی دوره دوم متوسطه | معلمان حق‌التدریس و جانشین کوتاه‌مدت | دستیاران آموزشی در آموزش عالی | کمک‌معلمان آموزش استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدیران آموزشی مقاطع ابتدایی و متوسطه | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | معلمان حق‌التدریس و جانشین کوتاه‌مدت | دستیاران آموزشی در آموزش عالی | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نظارت | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | راهبردهای یادگیری | نظارت | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | بیان کتبی | روانی و سیالی ایده‌ها | تمرکز بر نشانه‌های شنیداری | توجه انتخابی | استدلال استقرایی | ابتکار و اصالت | تقسیم توجه میان چند فعالیت | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | بیان کتبی | روانی ایده‌ها | توجه شنیداری | توجه انتخابی | استدلال استقرایی | اصالت | تقسیم توجه | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به عنوان زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | استادان علوم تربیتی آموزش عالی | مشاوران تحصیلی، شغلی و تربیتی | آموزگاران دوره ابتدایی (به‌جز استثنایی) | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مربیان پیش‌دبستانی (به‌جز استثنایی) | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | دبیران دوره دوم متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | معلمان استثنایی دوره ابتدایی | معلمان استثنایی دوره پیش‌دبستانی | معلمان استثنایی دوره اول متوسطه | معلمان استثنایی دوره مهدکودک | معلمان استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز استثنایی) | مدیران آموزش و بهسازی منابع انسانی | مدرسان و معلمان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | دستیاران آموزشی در آموزش عالی | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | مدیران آموزش و بهسازی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | رایانه و الکترونیک | ریاضیات</t>
+          <t>زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | دید نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | ابتکار و اصالت | روانی و سیالی ایده‌ها | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | وضوح گفتار | بیان کتبی | بینایی نزدیک | تشخیص گفتار | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | اصالت | روانی ایده‌ها | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مربیان سوادآموزی بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به عنوان زبان دوم | استادان و مدرسان علوم زیستی آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای دوره اول متوسطه | معلمان آموزش‌های فنی و حرفه‌ای دوره دوم متوسطه | استادان علوم تربیتی آموزش عالی | آموزگاران دوره ابتدایی (به‌جز استثنایی) | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان علم اطلاعات و دانش‌شناسی آموزش عالی | استادان علوم ریاضی آموزش عالی | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | استادان روان‌شناسی آموزش عالی | دبیران دوره دوم متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | استادان جامعه‌شناسی آموزش عالی | معلمان استثنایی دوره ابتدایی | معلمان استثنایی دوره پیش‌دبستانی | معلمان استثنایی دوره اول متوسطه | معلمان استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز استثنایی) | کمک‌معلمان آموزش استثنایی | مدرسان و معلمان خصوصی</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | معلمان آموزش‌های فنی و حرفه‌ای در دوره اول متوسطه | هنرآموزان و معلمان فنی‌وحرفه‌ای و کاردانش دوره دوم متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان روان‌شناسی دانشگاه | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | استادان جامعه‌شناسی دانشگاه | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره اول متوسطه | دبیران آموزش استثنایی دوره دوم متوسطه | کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | معلمان خصوصی و مدرسان تقویتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | رایانه و الکترونیک | ریاضیات</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه میان چند فعالیت | چابکی انگشتان | چابکی دستی | دید دور | حافظه و به‌خاطرسپاری | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز استثنایی) | کمک‌معلمان آموزش استثنایی | دستیاران آموزشی در آموزش عالی | مدرسان و معلمان خصوصی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مدرسان دوره‌های آزاد و مهارت‌آموزی | آموزگاران دوره ابتدایی (به‌جز استثنایی) | مربیان مهدکودک (به‌جز استثنایی) | مربیان پیش‌دبستانی (به‌جز استثنایی) | دبیران دوره اول متوسطه (به‌جز استثنایی و فنی‌وحرفه‌ای) | معلمان استثنایی دوره ابتدایی | سایر معلمان آموزش استثنایی | کاردان‌ها و تکنسین‌های کتابداری | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | مربیان و مراقبان کودک | کاردان‌ها و دستیاران خدمات اجتماعی و انسانی | مشاوران تحصیلی، شغلی و تربیتی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | سایر معلمان و مدرسان | سایر کارکنان حوزه آموزش و کتابداری</t>
+          <t>کمک‌معلمان دوره‌های پیش‌دبستانی، ابتدایی، دوره اول و دوم متوسطه (به‌جز آموزش استثنایی) | کمک‌معلمان آموزش استثنایی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | معلمان آموزش استثنایی دوره ابتدایی | معلمان آموزش استثنایی، سایر عناوین | تکنسین‌های کتابداری | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | مربیان و مراقبان کودک | دستیاران خدمات اجتماعی و انسانی | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان و مربیان آموزشی، سایر مشاغل | سایر کارکنان خدمات آموزشی و کتابداری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه میان چند فعالیت | چابکی انگشتان | چابکی دستی | دید دور | حافظه و به‌خاطرسپاری | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کتابداری | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | آرشیوداران | موزه‌داران | کاردان‌ها و مرمت‌کاران موزه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | سایر کمک‌معلمان و دستیاران آموزشی | دستیاران آموزشی در آموزش عالی | مدرسان و معلمان خصوصی | مدرسان دوره‌های آزاد و مهارت‌آموزی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | سایر معلمان و مدرسان | سایر مدیران آموزشی | مدیران آموزش عالی | مشاوران تحصیلی، شغلی و تربیتی | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان مدیریت اسناد و مدارک | کارمندان امور اداری و دفتری | سایر متصدیان اطلاعات و ثبت سوابق | کاردان‌ها و دستیاران خدمات اجتماعی و انسانی</t>
+          <t>تکنسین‌های کتابداری | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | کارشناسان اسناد و آرشیو | موزه‌داران | تکنسین‌ها و مرمت‌گران موزه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | سایر کمک‌معلمان و دستیاران آموزشی | دستیاران آموزشی در آموزش عالی | معلمان خصوصی و مدرسان تقویتی | مربیان دوره‌های آزاد و مهارت‌آموزی فردی | معلمان حق‌التدریس و جانشین کوتاه‌مدت | معلمان و مربیان آموزشی، سایر مشاغل | مدیران آموزشی، سایر موارد | مدیران آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان آموزش و توسعه منابع انسانی | کارشناسان مدیریت اسناد و مدارک | متصدیان امور دفتری و امور عمومی اداری | سایر متصدیان ثبت اسناد و اطلاعات | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | زبان انگلیسی | رایانه و الکترونیک | هنرهای تجسمی | ارتباطات و رسانه | فروش و بازاریابی | خدمات مشتریان و خدمات فردی</t>
+          <t>طراحی | زبان انگلیسی | رایانه و الکترونیک | هنرهای زیبا | ارتباطات و رسانه | فروش و بازاریابی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ابتکار و اصالت | روانی و سیالی ایده‌ها | درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | تجسم فضایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | تشخیص رنگ‌ها | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | بیان کتبی | دید دور | انعطاف‌پذیری در ادراک الگوها</t>
+          <t>اصالت | روانی ایده‌ها | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تجسم | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص رنگ بصری | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | طراحان مد و لباس | تدوین‌گران فیلم و ویدئو | هنرمندان هنرهای تجسمی (نقاشان، مجسمه‌سازان و تصویرگران) | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی | طراحان گرافیک | مدیران پروژه‌های فناوری اطلاعات | مدیران تامین و تولید برنامه‌های رسانه‌ای | مدیران فنی تولیدات چندرسانه‌ای | طراحان چیدمان و دکوراتورهای ویترین | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | کارشناسان مدیریت پروژه | کارشناسان روابط عمومی | طراحان صحنه و دکور | پویانماها و طراحان جلوه‌های ویژه | نویسندگان متون فنی | طراحان بازی‌های رایانه‌ای | طراحان رابط کاربری و صفحات وب | نویسندگان و پدیدآورندگان</t>
+          <t>هنرمندان صنایع دستی | طراحان مد و پوشاک | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | طراحان گرافیک | مدیران پروژه‌های فناوری اطلاعات | مدیران برنامه‌ریزی و پخش رسانه | مدیران فنی رسانه | طراحان دکوراسیون و ویترین مغازه | شاعران، ترانه‌سرایان و نویسندگان خلاق | تهیه‌کنندگان و کارگردانان | کارشناسان مدیریت پروژه | کارشناسان روابط عمومی | طراحان صحنه و نمایشگاه | پویانماها و طراحان جلوه‌های ویژه | نویسندگان متون فنی | طراحان بازی‌های ویدیویی | طراحان وب و رابط‌های دیجیتال | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | هنرهای تجسمی | فروش و بازاریابی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید و فراوری</t>
+          <t>طراحی | هنرهای زیبا | فروش و بازاریابی | زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ابتکار و اصالت | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دید نزدیک | روانی و سیالی ایده‌ها | تجسم فضایی | هماهنگی اندام‌های حرکتی | دقت کنترل حرکات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | تشخیص رنگ‌ها | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | درک کتبی | درک شفاهی | بیان شفاهی</t>
+          <t>اصالت | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | بینایی نزدیک | روانی ایده‌ها | تجسم | هماهنگی چند عضو | دقت کنترل | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | درک شفاهی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و درودگران کارگاهی | طراحان تجاری و صنعتی | قلم‌زنان، کلیشه‌سازان و حکاکان | الگوسازان پارچه و پوشاک | طراحان مد و لباس | هنرمندان هنرهای تجسمی (نقاشان، مجسمه‌سازان و تصویرگران) | رنگ‌کاران و پرداخت‌کاران چوب و مبلمان | طراحان گرافیک | طراحان دکوراسیون داخلی | جواهرسازان و سازندگان مصنوعات فلزات و سنگ‌های قیمتی | مدل‌سازان سازه‌های چوبی | قالب‌گیران، فرم‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | رنگ‌کاران، پوشش‌کاران و تزیین‌کاران صنعتی و دستی | الگوسازان قطعات فلزی و پلاستیکی | الگوسازان چوبی | کوزه‌گران و سفالگران کارگاهی | طراحان صحنه و دکور | دوزندگان دستی | دوزندگان و تعمیرکاران کفش و مصنوعات چرمی | سنگ‌تراشان و حکاکان سنگ در تولید صنعتی</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | طراحان تجاری و صنعتی | حکاکان و اسیدکاران | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | طراحان گرافیک | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | الگوسازان چوب | سفالگران خطوط تولید و کارگاهی | طراحان صحنه و نمایشگاه | دوزندگان دستی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان صنعتی سنگ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>یادگیری فعال | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>طراحی | رایانه و الکترونیک | زبان انگلیسی | تولید و فراوری | هنرهای تجسمی | آموزش و تدریس | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری</t>
+          <t>طراحی | رایانه و الکترونیک | زبان انگلیسی | تولید و فرآوری | هنرهای زیبا | آموزش و پرورش | ارتباطات و رسانه | خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ابتکار و اصالت | روانی و سیالی ایده‌ها | تجسم فضایی | ثبات دست و بازو | تشخیص رنگ‌ها | دید نزدیک | چابکی انگشتان | چابکی دستی | درک شفاهی | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | دید دور | درک کتبی</t>
+          <t>اصالت | روانی ایده‌ها | تجسم | ثبات دست و بازو | تشخیص رنگ بصری | بینایی نزدیک | مهارت انگشتان | مهارت دستی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | بینایی دور | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | صفحه‌آرایان و ناشران رومیزی | قلم‌زنان، کلیشه‌سازان و حکاکان | الگوسازان پارچه و پوشاک | طراحان مد و لباس | طراحان گرافیک | طراحان دکوراسیون داخلی | گریمورها و چهره‌پردازان نمایش و سینما | نقاشان ساختمان و تاسیسات | رنگ‌کاران، پوشش‌کاران و تزیین‌کاران صنعتی و دستی | الگوسازان قطعات فلزی و پلاستیکی | عکاسان | متصدیان ظهور و چاپ عکس و اپراتورهای لابراتوار | شاعران، ترانه‌سرایان و نویسندگان خلاق | کارشناسان و تکنسین‌های لیتوگرافی و پیش از چاپ | طراحان صحنه و دکور | پویانماها و طراحان جلوه‌های ویژه | طراحان بازی‌های رایانه‌ای</t>
+          <t>مدیران هنری | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | حکاکان و اسیدکاران | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | طراحان گرافیک | طراحان داخلی | چهره‌پردازان و گریموران تئاتر و سینما | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | عکاسان | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | شاعران، ترانه‌سرایان و نویسندگان خلاق | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | طراحان صحنه و نمایشگاه | پویانماها و طراحان جلوه‌های ویژه | طراحان بازی‌های ویدیویی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مخابرات | فنی و مهندسی | تولید و فراوری | جغرافیا</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | طراحی | ارتباطات و رسانه | خدمات مشتری و شخصی | فروش و بازاریابی | مخابرات | مهندسی و فناوری | تولید و فرآوری | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | تجسم فضایی | دید نزدیک | استدلال قیاسی | تشخیص رنگ‌ها | حساسیت به مسئله | وضوح گفتار | ابتکار و اصالت | بیان کتبی | مرتب‌سازی اطلاعات | روانی و سیالی ایده‌ها | استدلال استقرایی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تجسم | بینایی نزدیک | استدلال قیاسی | تشخیص رنگ بصری | حساسیت به مسئله | وضوح گفتار | اصالت | بیان کتبی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | استدلال استقرایی | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران هنری | تکنسین‌های صوت و تصویر | فیلم‌برداران تلویزیون، ویدئو و سینما | طراحان تجاری و صنعتی | برنامه‌نویسان رایانه | هنرمندان صنایع دستی | صفحه‌آرایان و ناشران رومیزی | تدوین‌گران فیلم و ویدئو | هنرمندان هنرهای تجسمی (نقاشان، مجسمه‌سازان و تصویرگران) | طراحان گرافیک | مدیران فنی تولیدات چندرسانه‌ای | عکاسان | متصدیان ظهور و چاپ عکس و اپراتورهای لابراتوار | کارشناسان و تکنسین‌های لیتوگرافی و پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های صدابرداری و مهندسی صدا | طراحان بازی‌های رایانه‌ای | توسعه‌دهندگان وب | طراحان رابط کاربری و صفحات وب | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران هنری | تکنسین‌های تجهیزات صوتی و تصویری | تصویربرداران تلویزیون، ویدیو و سینما | طراحان تجاری و صنعتی | برنامه‌نویسان کامپیوتر | هنرمندان صنایع دستی | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | مدیران فنی رسانه | عکاسان | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا | طراحان بازی‌های ویدیویی | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
